--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Synapse, Databricks, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=77bc67350b6fe349</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AXIOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery, Dask, Python</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,77 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab406fdc25efa811</t>
+          <t>https://www.indeed.com/viewjob?jk=615df761a4f7bebe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AXIOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f8df951309470c</t>
+          <t>https://www.indeed.com/viewjob?jk=723f07902d0a1dbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13e352cab8992d2c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,140 +468,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Synapse, Databricks, Power BI</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Hadoop, PostgreSQL, MySQL, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bc67350b6fe349</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>AI-agent engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615df761a4f7bebe</t>
+          <t>https://www.indeed.com/viewjob?jk=58187031da864ba5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723f07902d0a1dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Cloud and AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd43b753ced7eda4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13e352cab8992d2c</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327bd44a5b9fe387</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>33.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Hadoop, PostgreSQL, MySQL, Tableau</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, Glue</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-agent engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58187031da864ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Asset &amp; Wealth Management-Full Stack Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=9aac95b8620ff52b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Copilot, Cortex, S3, Data Lake, CI/CD, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud and AI Infrastructure Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Lake, Docker, Kubernetes, Databricks, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,322 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd43b753ced7eda4</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Laurate LLC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60a64e3d33dcdbbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=327bd44a5b9fe387</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cf10fec99dc5b34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=443a2031f17f5a0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f46c435f5923e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2092bc701501e519</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Kinesis, MLflow, PySpark, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Salesforce Financial Services Cloud Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.3</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, Glue</t>
+          <t>RAG, S3, EC2, Redshift, BigQuery, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=452ad96763321f8b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Cloud IAM Engineer (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RAG, S3, EC2, Redshift, BigQuery, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=4824fb9c6cc39b44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Full Stack Engineer-Associate-Dallas</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Cortex, EC2, Redshift, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aac95b8620ff52b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Copilot, Cortex, S3, Data Lake, CI/CD, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=123a097e3d92858f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Full Stack Golang Engineer (AWS | Python | React/Angular/Vue)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, Databricks, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8c7a7f43e72aac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d5c1c2e717f845</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Lakehouse Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Middletown, RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python</t>
+          <t>RAG, Prompt Engineering, S3, Glue, Data Lake, Kubernetes, Git, Kafka, Hadoop, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python</t>
+          <t>RAG, Gemini, Redshift, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Laurate LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a64e3d33dcdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
+          <t>Data Lake, Docker, Kubernetes, Databricks, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf10fec99dc5b34</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443a2031f17f5a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd21204e38d8804</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Glue, Athena, Data Lake, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f46c435f5923e4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Lake, Docker, Kubernetes, Databricks, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,1337 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2092bc701501e519</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Docker, Jenkins, Git, Databricks, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, spaCy, FastAPI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89e7a0fe8759e1dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer III - GenAI, AWS, Java/Python</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, Keras, CI/CD, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b74da9fe441a3d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI/ML SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Peraton</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Annapolis Junction, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f5cddc4a1d7b0ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07ed243abbfab05f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SOFTWARE ENGINEER - AGENTIC AI PLATFORM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Peraton</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Annapolis Junction, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf45004859d22b82</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Cloud Compliance &amp; Audit Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4497b12386af7b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Cloud Governance Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Junior Cloud Security Analyst</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cce2f36d56ea5ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Gemini, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d28c93aa6aa27747</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df738575d381ab95</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a8913b77031f744</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Data Lake, Kinesis, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d14ab6635d4caad</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Data Lake, Kinesis, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1192259c09a9ad04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, S3, Redshift, CI/CD, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94c1202d59cc7b16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, MySQL, MongoDB, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e378a9b0919f80e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, Git, Kafka, Hadoop, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=845d7cb4f2862288</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Engineer (GTM)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, Snowflake, BigQuery, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d06b129deaf2329</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LVT (LiveView Technologies)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>American Fork, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed1ba43ba400d50</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Copilot, Data Lake, CI/CD, Git, Databricks, NoSQL, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=991e75c73bbdc881</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Cloud Migration Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, Snowflake, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4e4644c6c71e01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Identity AI / ML Engineer</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Kinesis, MLflow, PySpark, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e3e12381ae3a0cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e61ddbe0c3515bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=502764fa99d2d1e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae146d3ea8e6d143</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Castleton Tower</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c986219937c2a5c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Regional Senior Solutions Architect | Data &amp; Analytics (Remote)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fddc1112a8cb8955</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Regional Senior Solutions Architect | Data &amp; Analytics (Remote)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7672d536e3772e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Scientist, PREDDICT Project</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Spaulding Rehabilitation Hospital</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7fb8f99d205ec03</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Salesforce Financial Services Cloud Consultant</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Redshift, BigQuery, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452ad96763321f8b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud IAM Engineer (AWS, Azure, GCP)</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Redshift, BigQuery, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, BigQuery, Dataflow, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4824fb9c6cc39b44</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Cortex, EC2, Redshift, FastAPI, Docker, CI/CD</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, BigQuery, Dataflow, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Python AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Velosys</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, TensorFlow, PyTorch</t>
+          <t>AI Engineer, RAG, LLaMA, Azure ML, S3, Docker, Kubernetes, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123a097e3d92858f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2270da88bd1034</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Golang Engineer (AWS | Python | React/Angular/Vue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8c7a7f43e72aac</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Terraform</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d5c1c2e717f845</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Lakehouse Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>TubeScience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Middletown, RI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Glue, Data Lake, Kubernetes, Git, Kafka, Hadoop, MongoDB</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
+          <t>https://www.indeed.com/viewjob?jk=386af4fb4867f398</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Redshift, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,277 +741,277 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=759cba5da6707bc7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, Databricks, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd21204e38d8804</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glue, Athena, Data Lake, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, Python</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, Databricks, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL, MongoDB, Python</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Docker, Jenkins, Git, Databricks, PostgreSQL, Python</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist, Identity Graph</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, spaCy, FastAPI, Git, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, AKS, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e7a0fe8759e1dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b93d88286f10bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka, Python</t>
+          <t>AI Engineer, RAG, Prompt Engineering, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - GenAI, AWS, Java/Python</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, Keras, CI/CD, Python, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74da9fe441a3d79</t>
+          <t>https://www.indeed.com/viewjob?jk=71a793e555fbf188</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI/ML SOFTWARE ENGINEER</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5cddc4a1d7b0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=81b329ed176cc8b9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>RAG, S3, Snowflake, Databricks, PySpark, Tableau, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07ed243abbfab05f</t>
+          <t>https://www.indeed.com/viewjob?jk=2432eb1112de42c5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER - AGENTIC AI PLATFORM</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Matrix Medical Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Bellaire, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Copilot, Prompt Engineering, Glue, Git, Power BI, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf45004859d22b82</t>
+          <t>https://www.indeed.com/viewjob?jk=fc55ef6084f57731</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Compliance &amp; Audit Engineer</t>
+          <t>Data Scientist III- Human Capital Data and Analytics Enablement</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Git, Snowflake, Hadoop, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4497b12386af7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=6941160617103aa0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Remote Sensing Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=a328f4601816f6e7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AI Solutions Architect, Digital Technology Solutions</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University Of Cincinnati</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Cortex, Git, Snowflake, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d1b120320d0365</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior AI ML Scientist - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+          <t>Generative AI, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce2f36d56ea5ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=12fb23373d5e08c2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Engineer - Test Automation, CI/CD, and DevOps</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gemini, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=8d4b02157385ec0c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28c93aa6aa27747</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8652cefda22a53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Citian</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,812 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df738575d381ab95</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Traba</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8913b77031f744</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect | AI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Trace3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect | AI</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Trace3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect | AI</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Trace3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect | AI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Trace3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Teradata</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Data Lake, Kinesis, Kubernetes, Terraform, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d14ab6635d4caad</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Teradata</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Data Lake, Kinesis, Kubernetes, Terraform, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1192259c09a9ad04</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, S3, Redshift, CI/CD, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94c1202d59cc7b16</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, MySQL, MongoDB, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e378a9b0919f80e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, Kubernetes, Git, Kafka, Hadoop, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=845d7cb4f2862288</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Engineer (GTM)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Data Lake, Snowflake, BigQuery, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d06b129deaf2329</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>LVT (LiveView Technologies)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>American Fork, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed1ba43ba400d50</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DOCSIS Testing Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Copilot, Data Lake, CI/CD, Git, Databricks, NoSQL, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=991e75c73bbdc881</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Cloud Migration Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Cortex, Snowflake, Tableau, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4e4644c6c71e01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Identity AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3e12381ae3a0cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Traba</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e61ddbe0c3515bc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=502764fa99d2d1e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae146d3ea8e6d143</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Castleton Tower</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Data Scientist, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Teradata</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c986219937c2a5c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Regional Senior Solutions Architect | Data &amp; Analytics (Remote)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Trace3</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fddc1112a8cb8955</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Regional Senior Solutions Architect | Data &amp; Analytics (Remote)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Trace3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7672d536e3772e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Scientist, PREDDICT Project</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Spaulding Rehabilitation Hospital</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7fb8f99d205ec03</t>
+          <t>https://www.indeed.com/viewjob?jk=ae75d5c01d2807f2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, BigQuery, Dataflow, Databricks, BigQuery</t>
+          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, BigQuery, Dataflow, Databricks, BigQuery</t>
+          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Python AI Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Velosys</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Azure ML, S3, Docker, Kubernetes, Git, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2270da88bd1034</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka, Tableau, Power BI</t>
+          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>23.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Generative AI / LLM Engineering Fellow (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TubeScience</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386af4fb4867f398</t>
+          <t>https://www.indeed.com/viewjob?jk=718d6addfb3cba74</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Glue, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759cba5da6707bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>Generative AI, RAG, GitHub Actions, Git, Snowflake, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Software Engineer - Document Generation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c88ef97204165d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Backend Engineer (Infrastructure &amp; DevOps Focus)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=a62537a1b62efc7e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Southern Motor Carriers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Peachtree City, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f11162638fb256</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Southern Motor Carriers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Peachtree City, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b99940ba7d839f82</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Identity Graph</t>
+          <t>Software Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, AKS, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b93d88286f10bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a349add3612b491c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd668292178bbfb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a793e555fbf188</t>
+          <t>https://www.indeed.com/viewjob?jk=789ec2cf44cba17a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b329ed176cc8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b99f3a1e0b6cc766</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,297 +1151,822 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Snowflake, Databricks, PySpark, Tableau, Power BI, Quicksight, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432eb1112de42c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d79cc88772a4daed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Matrix Medical Management</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellaire, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Glue, Git, Power BI, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc55ef6084f57731</t>
+          <t>https://www.indeed.com/viewjob?jk=77b0a1b26cd283dc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist III- Human Capital Data and Analytics Enablement</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Snowflake, Hadoop, NoSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6941160617103aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f543e454945f31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Remote Sensing Data Scientist</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a328f4601816f6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e3cca8bd11da2c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Solutions Architect, Digital Technology Solutions</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University Of Cincinnati</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Cortex, Git, Snowflake, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d1b120320d0365</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0daba23bdc766e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI ML Scientist - Remote</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fb23373d5e08c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8efaf26f8bbdfcc1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation, CI/CD, and DevOps</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d4b02157385ec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec6204e157e382cd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8652cefda22a53</t>
+          <t>https://www.indeed.com/viewjob?jk=13b2e081670e5181</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a450b3abc917109c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e39a2acfe0c2542</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c580bbf29c995240</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Washington, DC, US USA</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=639a4cd3c4899432</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3b1860cd6dd27e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nature's Sunshine Products</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff358ad9f0da0f27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Product Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, S3, MLflow, Docker, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa6d65672e611893</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FastAPI, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Java Full Stack</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae75d5c01d2807f2</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=705e68c1c4bdc01b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Java Full Stack</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=784d5ee085de95cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05bb2291289b80ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfb67d912d053c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66c5dc275cdb941e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52b7e19201dd3923</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hoffman &amp; Hoffman Inc</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e45341f9cc53e4f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Science Graduate Summer Intern (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Snowflake, Redshift, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f66c9d430d56db47</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-27.xlsx
+++ b/daily_matches/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>Data Scientist, RAG, Cortex, S3, Glue, Redshift, Data Lake, Kinesis, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Full Stack Software Development Engineer - AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Mistral, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>SF Technology - Software Engineering - Senior Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>RAG, S3, Glue, Kinesis, FastAPI, Docker, Terraform, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Generative AI / LLM Engineering Fellow (Remote)</t>
+          <t>AI Engineer – GenAI, Autonomous Agents &amp; Data Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718d6addfb3cba74</t>
+          <t>https://www.indeed.com/viewjob?jk=624fd46feb116d1f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer – GenAI, Autonomous Agents &amp; Data Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glue, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=86a280fb29296128</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>AI Engineer – GenAI, Autonomous Agents &amp; Data Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d42895b2a51de5b8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - Core Platform</t>
+          <t>AI Engineer – GenAI, Autonomous Agents &amp; Data Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, GitHub Actions, Git, Snowflake, MySQL, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+          <t>https://www.indeed.com/viewjob?jk=b792bbf8622c49a5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Document Generation</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Prompt Engineering, S3, Redshift, Redshift, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c88ef97204165d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a908ffaef60768e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Backend Engineer (Infrastructure &amp; DevOps Focus)</t>
+          <t>ML / AI Engineer – MLOps &amp; GenAI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62537a1b62efc7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7385d838a840a4b6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>ML / AI Engineer – MLOps &amp; GenAI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Southern Motor Carriers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peachtree City, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f11162638fb256</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcc966e37800328</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>ML / AI Engineer – MLOps &amp; GenAI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southern Motor Carriers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Peachtree City, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b99940ba7d839f82</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdac1af1495286d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML / AI Engineer – MLOps &amp; GenAI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a113680000317a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Automation Engineer</t>
+          <t>GenAI &amp; Agentic AI Engineer – Enterprise AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,199 +1021,199 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a349add3612b491c</t>
+          <t>https://www.indeed.com/viewjob?jk=0741988c9d85739a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>GenAI &amp; Agentic AI Engineer – Enterprise AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd668292178bbfb</t>
+          <t>https://www.indeed.com/viewjob?jk=8c70bcbc4ae2511d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>GenAI &amp; Agentic AI Engineer – Enterprise AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789ec2cf44cba17a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb34a7301b39fa2c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>GenAI &amp; Agentic AI Engineer – Enterprise AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Erie Heights, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b99f3a1e0b6cc766</t>
+          <t>https://www.indeed.com/viewjob?jk=189b22ccb6ee5901</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Private Markets Data Analyst/Senior Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Snowflake, PySpark, MySQL, MongoDB, Tableau, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79cc88772a4daed</t>
+          <t>https://www.indeed.com/viewjob?jk=59dbaa3bccc08fd1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b0a1b26cd283dc</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f543e454945f31</t>
+          <t>https://www.indeed.com/viewjob?jk=ae43ae3ce91a42d3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior AI / ML Engineer – Enterprise Data &amp; GenAI Solutions - AIRLHV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e3cca8bd11da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=181b17280c6c9b51</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior AI / ML Engineer – Enterprise Data &amp; GenAI Solutions - AIRLHV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0daba23bdc766e</t>
+          <t>https://www.indeed.com/viewjob?jk=a28d6c7b0e0445ea</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior AI / ML Engineer – Enterprise Data &amp; GenAI Solutions - AIRLHV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efaf26f8bbdfcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2be4c320d5903f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior AI / ML Engineer – Enterprise Data &amp; GenAI Solutions - AIRLHV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>LangChain, RAG, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec6204e157e382cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3b2d3a50157f19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior Data Engineer – Cloud &amp; AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b2e081670e5181</t>
+          <t>https://www.indeed.com/viewjob?jk=2d191583ed6797b2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior Data Engineer – Cloud &amp; AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a450b3abc917109c</t>
+          <t>https://www.indeed.com/viewjob?jk=302491032b48aff8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior Data Engineer – Cloud &amp; AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e39a2acfe0c2542</t>
+          <t>https://www.indeed.com/viewjob?jk=8b84b1bb58eacf92</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Senior Data Engineer – Cloud &amp; AI Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, PyTorch, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c580bbf29c995240</t>
+          <t>https://www.indeed.com/viewjob?jk=2717b5399d14fcf7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Applied AI Scientist III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639a4cd3c4899432</t>
+          <t>https://www.indeed.com/viewjob?jk=73429e0c02070d48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Project Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Mayfield Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b1860cd6dd27e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a381f7c3301d78fe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nature's Sunshine Products</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, SQL, R, Scala, Optimization</t>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, Kafka, Hadoop, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff358ad9f0da0f27</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Product Solutions Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, S3, MLflow, Docker, CI/CD, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6d65672e611893</t>
+          <t>https://www.indeed.com/viewjob?jk=429b47169e98dc38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Engineer – GenAI, MLOps &amp; Cloud Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FastAPI, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdf6308159fe358</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Java Full Stack</t>
+          <t>AI Engineer – GenAI, MLOps &amp; Cloud Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705e68c1c4bdc01b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b892026d78af43d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Java Full Stack</t>
+          <t>AI Engineer – GenAI, MLOps &amp; Cloud Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784d5ee085de95cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3bad41236b4ad420</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Platform Engineer</t>
+          <t>AI Engineer – GenAI, MLOps &amp; Cloud Platforms - AIRLHV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bb2291289b80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b8628b4a149e0d33</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Platform Engineer</t>
+          <t>Senior Software Engineer, Identity and Access Management</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>RAG, Athena, CI/CD, Jenkins, Terraform, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb67d912d053c12</t>
+          <t>https://www.indeed.com/viewjob?jk=2abbb930e5a1c278</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Platform Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Goodwin Procter LLP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c5dc275cdb941e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1250b3ec3ebce2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Platform Engineer</t>
+          <t>Senior Data Scientist, StreeyEasy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Zillow</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Databricks, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b7e19201dd3923</t>
+          <t>https://www.indeed.com/viewjob?jk=b7bd52f596798a7b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Software Test Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hoffman &amp; Hoffman Inc</t>
+          <t>Particle Measuring Systems</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Niwot, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45341f9cc53e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=cddf9df56337771e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Science Graduate Summer Intern (Summer 2026)</t>
+          <t>Applied Data Scientist (Contract)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Civis Analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Snowflake, Redshift, Python, SQL, R, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, Gemini, Git, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,217 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66c9d430d56db47</t>
+          <t>https://www.indeed.com/viewjob?jk=92fde6105c9fe233</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Applied Data Scientist (Contract)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Civis Analytics</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb6790ee3984fcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Applied Data Scientist (Contract)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Civis Analytics</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f11be2e7b307b9f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics (ML-Enabled Systems)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, Data Lake, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3ae5f03d43c8a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NRG Energy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, S3, Git, Databricks, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III -Python Fullstack - AI/ML</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d71b09329014630</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer - Playwright (Contract)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mindcubed</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6c007a75e5d3483</t>
         </is>
       </c>
     </row>
